--- a/data/in/WeatherData_ThermalLandscapes_curated.xlsx
+++ b/data/in/WeatherData_ThermalLandscapes_curated.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peter\Dropbox\Davies_Lab\Documents\ThermalLandscapesProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d208f1c5c7e8ef3/Documents/Python/ThermalLandscapes/data/in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7D8F5B-0C01-4137-9B97-113E0EF55A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{6E7D8F5B-0C01-4137-9B97-113E0EF55A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2679E0A-FF13-41D8-9581-8D1F74DA422D}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{B4E39C6E-1CC0-4BBA-8DDC-D90252A6E433}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B4E39C6E-1CC0-4BBA-8DDC-D90252A6E433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="50">
   <si>
     <t>Station</t>
   </si>
@@ -278,9 +279,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -318,7 +319,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -424,7 +425,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -566,7 +567,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -579,7 +580,8 @@
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="3" max="3" width="15" hidden="1" customWidth="1"/>
+    <col min="4" max="22" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -10764,4 +10766,95 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87AD5EC-2F07-4875-AA39-4A1BFE730F60}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6">
+        <v>43846</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6">
+        <v>43851</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6">
+        <v>43852</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="6">
+        <v>43854</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6">
+        <v>44168</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="6">
+        <v>44172</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>